--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484717_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484717_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6286</v>
+        <v>5.7484</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1662</v>
+        <v>5.5077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4624</v>
+        <v>0.2407</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7412</v>
+        <v>7.5256</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6218</v>
+        <v>2.4425</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1194</v>
+        <v>5.0831</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5836</v>
+        <v>7.132</v>
       </c>
       <c r="K2" t="n">
-        <v>5.378</v>
+        <v>3.175</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2057</v>
+        <v>3.957</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8424</v>
+        <v>0.3936</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7561</v>
+        <v>-0.7325</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0863</v>
+        <v>1.1261</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5661</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3402</v>
+        <v>0.2228</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4319</v>
+        <v>0.4514</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9083</v>
+        <v>-0.2286</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.019</v>
+        <v>-1.2452</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2828</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2999</v>
+        <v>5.5111</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0592</v>
+        <v>5.4455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2407</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5256</v>
+        <v>3.7412</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4425</v>
+        <v>3.6218</v>
       </c>
       <c r="I3" t="n">
-        <v>5.0831</v>
+        <v>0.1194</v>
       </c>
       <c r="J3" t="n">
-        <v>7.132</v>
+        <v>5.5836</v>
       </c>
       <c r="K3" t="n">
-        <v>3.175</v>
+        <v>5.378</v>
       </c>
       <c r="L3" t="n">
-        <v>3.957</v>
+        <v>0.2057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3936</v>
+        <v>-1.8424</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7325</v>
+        <v>-1.7561</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1261</v>
+        <v>-0.0863</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0757</v>
+        <v>-1.1322</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2257</v>
+        <v>1.2227</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0029</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2286</v>
+        <v>0.5115</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2452</v>
+        <v>-0.019</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1729</v>
+        <v>4.6092</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4819</v>
+        <v>4.8918</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.309</v>
+        <v>-0.2826</v>
       </c>
       <c r="G4" t="n">
         <v>1.1233</v>
@@ -766,13 +766,13 @@
         <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1957</v>
+        <v>0.2406</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09</v>
+        <v>0.3199</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1057</v>
+        <v>-0.0793</v>
       </c>
       <c r="V4" t="n">
         <v>1.547</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5209</v>
+        <v>2.4932</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6809</v>
+        <v>3.5884</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.16</v>
+        <v>-1.0951</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1666</v>
+        <v>4.582</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2029</v>
+        <v>2.0927</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9637</v>
+        <v>2.4894</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6521</v>
+        <v>6.9284</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4722</v>
+        <v>3.7032</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1799</v>
+        <v>3.2252</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4855</v>
+        <v>-2.3464</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2693</v>
+        <v>-1.6106</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2162</v>
+        <v>-0.7358</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9393</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2556</v>
+        <v>0.4531</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6838</v>
+        <v>-0.5225</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.585</v>
+        <v>1.566</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3398</v>
+        <v>0.9244</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2452</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7356</v>
+        <v>2.2027</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0424</v>
+        <v>2.7066</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3068</v>
+        <v>-0.5039</v>
       </c>
       <c r="G6" t="n">
-        <v>4.582</v>
+        <v>3.1666</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0927</v>
+        <v>1.2029</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4894</v>
+        <v>1.9637</v>
       </c>
       <c r="J6" t="n">
-        <v>6.9284</v>
+        <v>4.6521</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7032</v>
+        <v>2.4722</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2252</v>
+        <v>2.1799</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3464</v>
+        <v>-1.4855</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6106</v>
+        <v>-1.2693</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7358</v>
+        <v>-0.2162</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.5853</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.7175</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8270999999999999</v>
+        <v>0.6211</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0929</v>
+        <v>0.2812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7342</v>
+        <v>0.3399</v>
       </c>
       <c r="V6" t="n">
-        <v>1.566</v>
+        <v>-1.585</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9244</v>
+        <v>-0.3398</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6744</v>
+        <v>2.0687</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8131</v>
+        <v>2.9694</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1387</v>
+        <v>-0.9006</v>
       </c>
       <c r="G7" t="n">
         <v>2.4469</v>
@@ -1000,13 +1000,13 @@
         <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7724</v>
+        <v>-0.3781</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2039</v>
+        <v>0.3602</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9764</v>
+        <v>-0.7383</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5915</v>
+        <v>1.5279</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3635</v>
+        <v>0.0944</v>
       </c>
       <c r="F8" t="n">
-        <v>0.228</v>
+        <v>1.4335</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0997</v>
+        <v>0.3883</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4891</v>
+        <v>-0.3044</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5889</v>
+        <v>0.6927</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6058</v>
+        <v>0.7472</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8227</v>
+        <v>0.6394</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2169</v>
+        <v>0.1078</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7055</v>
+        <v>-0.3589</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3335</v>
+        <v>-0.9438</v>
       </c>
       <c r="O8" t="n">
-        <v>0.628</v>
+        <v>0.5849</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5661</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3139</v>
+        <v>0.4981</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9464</v>
+        <v>0.1776</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3675</v>
+        <v>0.3204</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8065</v>
+        <v>1.1787</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2567</v>
+        <v>1.1888</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0631</v>
+        <v>-0.0101</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3883</v>
+        <v>-0.0997</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3044</v>
+        <v>0.4891</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6927</v>
+        <v>-0.5889</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7472</v>
+        <v>0.6058</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6394</v>
+        <v>1.8227</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1078</v>
+        <v>-1.2169</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3589</v>
+        <v>-0.7055</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9438</v>
+        <v>-1.3335</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5849</v>
+        <v>0.628</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2234</v>
+        <v>0.901</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1735</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0499</v>
+        <v>0.1294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.428</v>
+        <v>0.4074</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4342</v>
+        <v>-0.3754</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8622</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3332</v>
@@ -1234,13 +1234,13 @@
         <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2198</v>
+        <v>-0.2404</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1205</v>
+        <v>0.1793</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3403</v>
+        <v>-0.4197</v>
       </c>
       <c r="V10" t="n">
         <v>0.6036</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.6635</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5352</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4813</v>
+        <v>-1.2961</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7802</v>
@@ -1312,13 +1312,13 @@
         <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.619</v>
+        <v>-0.3364</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2039</v>
+        <v>0.3014</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8229</v>
+        <v>-0.6378</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2452</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4623</v>
+        <v>-1.0461</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5443</v>
+        <v>-2.1546</v>
       </c>
       <c r="F12" t="n">
-        <v>1.082</v>
+        <v>1.1085</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2201</v>
@@ -1390,13 +1390,13 @@
         <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1352</v>
+        <v>0.5514</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1764</v>
+        <v>0.2134</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3116</v>
+        <v>0.338</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.4499</v>
+        <v>24.0377</v>
       </c>
       <c r="E13" t="n">
-        <v>23.9072</v>
+        <v>24.4952</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4574</v>
+        <v>-0.4572999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>20.5407</v>
@@ -1456,10 +1456,10 @@
         <v>-13.8282</v>
       </c>
       <c r="O13" t="n">
-        <v>2.600899999999999</v>
+        <v>2.6009</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.775557561562891e-16</v>
+        <v>-4.996003610813204e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.096</v>
@@ -1468,16 +1468,16 @@
         <v>15.096</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6455</v>
+        <v>3.2333</v>
       </c>
       <c r="T13" t="n">
-        <v>3.632299999999999</v>
+        <v>4.2204</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9867999999999998</v>
+        <v>-0.9870000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2638000000000003</v>
+        <v>0.2637999999999998</v>
       </c>
       <c r="W13" t="n">
         <v>3.6026</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7623</v>
+        <v>2.8553</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8812</v>
+        <v>4.712</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1189</v>
+        <v>-1.8567</v>
       </c>
       <c r="G14" t="n">
         <v>0.1164</v>
@@ -1546,13 +1546,13 @@
         <v>1.3209</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0005</v>
+        <v>0.0934</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8587</v>
+        <v>0.6895</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8582</v>
+        <v>-0.596</v>
       </c>
       <c r="V14" t="n">
         <v>1.5132</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5474</v>
+        <v>-0.3021</v>
       </c>
       <c r="E16" t="n">
-        <v>1.174</v>
+        <v>-1.104</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7214</v>
+        <v>0.802</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1773</v>
+        <v>-0.1161</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.2199</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2618</v>
+        <v>0.1038</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7723</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7184</v>
+        <v>0.1057</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0411</v>
+        <v>0.6666</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9369</v>
+        <v>-0.8883</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6339</v>
+        <v>-0.3256</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.303</v>
+        <v>-0.5628</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2486</v>
+        <v>-0.0728</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4144</v>
+        <v>0.0107</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1658</v>
+        <v>-0.0835</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9962</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9962</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7002</v>
+        <v>-0.6894</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3963</v>
+        <v>0.9791</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6962</v>
+        <v>-1.6685</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1161</v>
+        <v>-0.1773</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2199</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1038</v>
+        <v>-0.2618</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7723</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1057</v>
+        <v>0.7184</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6666</v>
+        <v>0.0411</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8883</v>
+        <v>-0.9369</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3256</v>
+        <v>-0.6339</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5628</v>
+        <v>-0.303</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4709</v>
+        <v>0.1067</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2816</v>
+        <v>0.2195</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1893</v>
+        <v>-0.1129</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.9962</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.9962</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>R. MOLLERMARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1016</v>
+        <v>-0.8041</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0642</v>
+        <v>-0.2482</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0375</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8212</v>
+        <v>-1.3153</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2443</v>
+        <v>-0.0814</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0656</v>
+        <v>-1.2339</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9398</v>
+        <v>-0.2426</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1396</v>
+        <v>0.4069</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1998</v>
+        <v>-0.6496</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.761</v>
+        <v>-1.0727</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8953</v>
+        <v>-0.4883</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8657</v>
+        <v>-0.5843</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3209</v>
+        <v>0.9435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8305</v>
+        <v>-0.1887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3233</v>
+        <v>-1.0549</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2039</v>
+        <v>-0.4395</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1194</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2828</v>
+        <v>0.6226</v>
       </c>
       <c r="W18" t="n">
         <v>0.6226</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. MOLLERMARK</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1289</v>
+        <v>-1.3574</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.443</v>
+        <v>2.9417</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6858</v>
+        <v>-4.2991</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3153</v>
+        <v>-2.4914</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0814</v>
+        <v>-0.5643</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2339</v>
+        <v>-1.9271</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2426</v>
+        <v>3.1852</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4069</v>
+        <v>2.5582</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6496</v>
+        <v>0.6269</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0727</v>
+        <v>-5.6766</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4883</v>
+        <v>-3.1225</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5843</v>
+        <v>-2.5541</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9435</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3797</v>
+        <v>0.0927</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6343</v>
+        <v>0.3043</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7454</v>
+        <v>-0.2116</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6226</v>
+        <v>1.7961</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6226</v>
+        <v>2.4714</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8311</v>
+        <v>-1.8363</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2879</v>
+        <v>-1.1616</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5432</v>
+        <v>-0.6747</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4019</v>
+        <v>-0.8212</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5790999999999999</v>
+        <v>1.2443</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8228</v>
+        <v>-2.0656</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4139</v>
+        <v>0.9398</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8028999999999999</v>
+        <v>2.1396</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2169</v>
+        <v>-1.1998</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.988</v>
+        <v>-1.761</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3821</v>
+        <v>-0.8953</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6059</v>
+        <v>-0.8657</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3774</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1934</v>
+        <v>0.5886</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2323</v>
+        <v>0.1065</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4257</v>
+        <v>0.4821</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3018</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1573</v>
+        <v>-2.098</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4545</v>
+        <v>-1.2879</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.6118</v>
+        <v>-0.8101</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4914</v>
+        <v>-2.4019</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5643</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9271</v>
+        <v>-1.8228</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1852</v>
+        <v>-0.4139</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5582</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6269</v>
+        <v>-1.2169</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.6766</v>
+        <v>-1.988</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.1225</v>
+        <v>-1.3821</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5541</v>
+        <v>-0.6059</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0192</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.0735</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1829</v>
+        <v>-0.2323</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5243</v>
+        <v>0.1588</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7961</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4714</v>
+        <v>0.3018</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6754</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3383</v>
+        <v>-3.0028</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4602</v>
+        <v>0.5576</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7985</v>
+        <v>-3.5604</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3554</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2281</v>
+        <v>0.1074</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1698</v>
+        <v>0.2673</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3979</v>
+        <v>-0.1598</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1295</v>
+        <v>-4.1349</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2349</v>
+        <v>-2.9722</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3644</v>
+        <v>-1.1626</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4677</v>
+        <v>-3.1993</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6366</v>
+        <v>-0.9868</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-2.2125</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06510000000000001</v>
+        <v>-0.4001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5501</v>
+        <v>-0.4171</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.485</v>
+        <v>0.017</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.5328</v>
+        <v>-2.7993</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.1867</v>
+        <v>-0.5697</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3461</v>
+        <v>-2.2295</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3209</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
         <v>1.5096</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3639</v>
+        <v>0.0835</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3585</v>
+        <v>-0.0436</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7224</v>
+        <v>0.127</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.6188</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.6188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8661</v>
+        <v>-4.2389</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.362</v>
+        <v>-0.0574</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5042</v>
+        <v>-4.1816</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1993</v>
+        <v>-3.4677</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9868</v>
+        <v>-2.6366</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2125</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4001</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4171</v>
+        <v>0.5501</v>
       </c>
       <c r="L24" t="n">
-        <v>0.017</v>
+        <v>-0.485</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7993</v>
+        <v>-3.5328</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5697</v>
+        <v>-3.1867</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2295</v>
+        <v>-0.3461</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R24" t="n">
         <v>1.5096</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6478</v>
+        <v>-0.4734</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4333</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2145</v>
+        <v>-0.5396</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.6188</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.6188</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4227</v>
+        <v>-6.5531</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0389</v>
+        <v>-1.7466</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.3838</v>
+        <v>-4.8065</v>
       </c>
       <c r="G25" t="n">
         <v>-4.2512</v>
@@ -2404,13 +2404,13 @@
         <v>1.5096</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3074</v>
+        <v>-0.4378</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.2146</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2297</v>
+        <v>-0.6525</v>
       </c>
       <c r="V25" t="n">
         <v>-1.298</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-23.4499</v>
+        <v>-22.1508</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4573</v>
+        <v>0.4572999999999996</v>
       </c>
       <c r="F26" t="n">
-        <v>-23.9072</v>
+        <v>-22.608</v>
       </c>
       <c r="G26" t="n">
         <v>-20.5407</v>
@@ -2482,19 +2482,19 @@
         <v>15.096</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6455</v>
+        <v>-1.3464</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9868000000000002</v>
+        <v>0.9868</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.6323</v>
+        <v>-2.3333</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2638999999999998</v>
       </c>
       <c r="W26" t="n">
-        <v>3.3388</v>
+        <v>3.338800000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-3.6028</v>
